--- a/assets/constructions/examples/ctd_tsmb_holderarbor.xlsx
+++ b/assets/constructions/examples/ctd_tsmb_holderarbor.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AH6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -579,11 +579,31 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MHCS-7-C4</t>
+          <t>MHCS-5-C4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -597,7 +617,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
         <v>40</v>
@@ -639,12 +659,12 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>VARGUS_D:7</t>
+          <t>VARGUS_D:5</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>VAR_MICR:7</t>
+          <t>VAR_MICR:5</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -665,11 +685,25 @@
           <t>2019 / Groovex Catalog</t>
         </is>
       </c>
+      <c r="AE2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>543.15</v>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>49933.79</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MHCS-6-C3</t>
+          <t>MHCS-4-C4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -683,22 +717,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H3" t="n">
-        <v>23.7</v>
+        <v>21.7</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
@@ -708,7 +742,7 @@
         <v>45</v>
       </c>
       <c r="Q3" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -720,17 +754,17 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>ISO_26623:32</t>
+          <t>ISO_26623:40</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>VARGUS_D:6</t>
+          <t>VARGUS_D:4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>VAR_MICR:6</t>
+          <t>VAR_MICR:4</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -751,11 +785,25 @@
           <t>2019 / Groovex Catalog</t>
         </is>
       </c>
+      <c r="AE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>543.15</v>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>49933.79</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MHCS-4-C4</t>
+          <t>MHCS-8-C4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -769,32 +817,32 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
         <v>40</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>16</v>
+        <v>21.5</v>
       </c>
       <c r="H4" t="n">
-        <v>21.7</v>
+        <v>24.5</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="Q4" t="n">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -811,12 +859,12 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>VARGUS_D:4</t>
+          <t>VARGUS_D:8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>VAR_MICR:4</t>
+          <t>VAR_MICR:8</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -837,11 +885,25 @@
           <t>2019 / Groovex Catalog</t>
         </is>
       </c>
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>543.15</v>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>49933.79</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MHCS-8-C4</t>
+          <t>MHCS-6-C4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -855,32 +917,32 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
         <v>40</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>21.5</v>
+        <v>20</v>
       </c>
       <c r="H5" t="n">
-        <v>24.5</v>
+        <v>23.7</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="Q5" t="n">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -897,12 +959,12 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>VARGUS_D:8</t>
+          <t>VARGUS_D:6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>VAR_MICR:8</t>
+          <t>VAR_MICR:6</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -923,11 +985,25 @@
           <t>2019 / Groovex Catalog</t>
         </is>
       </c>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>543.15</v>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>49933.79</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MHCS-8-C3</t>
+          <t>MHCS-7-C4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -941,29 +1017,29 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>21.5</v>
+        <v>20</v>
       </c>
       <c r="H6" t="n">
-        <v>24.5</v>
+        <v>23.7</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Q6" t="n">
         <v>74</v>
@@ -978,17 +1054,17 @@
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>ISO_26623:32</t>
+          <t>ISO_26623:40</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>VARGUS_D:8</t>
+          <t>VARGUS_D:7</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>VAR_MICR:8</t>
+          <t>VAR_MICR:7</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1008,6 +1084,20 @@
         <is>
           <t>2019 / Groovex Catalog</t>
         </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>543.15</v>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>49933.79</v>
       </c>
     </row>
   </sheetData>
